--- a/data/trans_bre/P57_AF_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 1,3</t>
+          <t>-12,98; 1,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 12,03</t>
+          <t>-5,01; 10,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 9,26</t>
+          <t>-4,18; 10,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -0,35</t>
+          <t>-12,3; 0,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 2,29</t>
+          <t>-20,92; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 22,37</t>
+          <t>-8,01; 19,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 14,29</t>
+          <t>-5,82; 15,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,49; -0,76</t>
+          <t>-22,51; 1,13</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 13,06</t>
+          <t>-1,42; 13,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 13,17</t>
+          <t>-1,97; 13,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 8,16</t>
+          <t>-5,52; 7,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 6,83</t>
+          <t>-6,39; 6,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 26,22</t>
+          <t>-2,38; 27,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 22,97</t>
+          <t>-3,02; 23,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 12,41</t>
+          <t>-7,69; 11,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 13,02</t>
+          <t>-10,8; 13,03</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 6,89</t>
+          <t>-9,77; 6,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 11,28</t>
+          <t>-3,75; 10,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 8,35</t>
+          <t>-7,45; 7,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 46,4</t>
+          <t>-3,3; 46,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 10,99</t>
+          <t>-14,64; 10,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 19,19</t>
+          <t>-5,91; 18,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 11,31</t>
+          <t>-9,61; 10,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 345,79</t>
+          <t>-5,54; 283,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 5,97</t>
+          <t>-3,5; 5,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,82</t>
+          <t>2,07; 11,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 3,43</t>
+          <t>-4,4; 3,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 26,49</t>
+          <t>-3,9; 23,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 9,61</t>
+          <t>-5,31; 9,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 17,38</t>
+          <t>3,1; 17,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 4,64</t>
+          <t>-5,75; 4,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 48,15</t>
+          <t>-6,62; 39,76</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 11,04</t>
+          <t>-2,75; 11,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 8,86</t>
+          <t>-2,58; 8,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 8,02</t>
+          <t>-0,88; 7,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 2,64</t>
+          <t>-20,9; 2,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 19,45</t>
+          <t>-3,94; 19,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 13,94</t>
+          <t>-3,64; 12,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 10,62</t>
+          <t>-1,12; 9,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 4,01</t>
+          <t>-31,07; 4,42</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 16,95</t>
+          <t>4,23; 16,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 18,18</t>
+          <t>5,71; 18,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 13,52</t>
+          <t>1,21; 13,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,77; 33,88</t>
+          <t>12,3; 34,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,49; 39,64</t>
+          <t>7,96; 39,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,64; 38,84</t>
+          <t>10,0; 38,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 20,95</t>
+          <t>1,73; 20,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,24; 132,84</t>
+          <t>27,93; 131,59</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,01</t>
+          <t>-1,77; 3,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,29</t>
+          <t>2,42; 7,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 4,16</t>
+          <t>0,05; 4,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 19,9</t>
+          <t>-0,49; 19,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 5,13</t>
+          <t>-2,84; 5,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 11,99</t>
+          <t>3,75; 12,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,74</t>
+          <t>0,07; 5,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 46,07</t>
+          <t>-0,92; 44,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AF_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,38</t>
+          <t>-6,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-12,41%</t>
+          <t>-11,96%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 1,51</t>
+          <t>-13,26; 1,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 10,29</t>
+          <t>-5,53; 10,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 10,2</t>
+          <t>-3,77; 9,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 0,36</t>
+          <t>-12,24; -0,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 2,68</t>
+          <t>-21,42; 2,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 19,23</t>
+          <t>-8,96; 18,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 15,61</t>
+          <t>-5,5; 14,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 1,13</t>
+          <t>-22,35; -1,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-2,76%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 13,3</t>
+          <t>-1,95; 12,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 13,25</t>
+          <t>-1,75; 12,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 7,64</t>
+          <t>-6,14; 7,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 6,74</t>
+          <t>-7,91; 4,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 27,02</t>
+          <t>-3,18; 25,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 23,3</t>
+          <t>-2,73; 22,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 11,33</t>
+          <t>-8,44; 11,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 13,03</t>
+          <t>-13,02; 8,39</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,66</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>-1,73%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 6,62</t>
+          <t>-9,44; 7,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 10,89</t>
+          <t>-3,5; 11,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 7,66</t>
+          <t>-6,29; 9,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 46,09</t>
+          <t>-7,96; 6,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 10,5</t>
+          <t>-14,02; 11,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 18,78</t>
+          <t>-5,45; 18,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 10,2</t>
+          <t>-7,83; 12,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 283,29</t>
+          <t>-13,35; 11,55</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>-1,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>-2,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 5,99</t>
+          <t>-3,31; 5,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 11,04</t>
+          <t>1,44; 10,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,62</t>
+          <t>-4,51; 3,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 23,37</t>
+          <t>-5,95; 2,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 9,46</t>
+          <t>-5,02; 9,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 17,32</t>
+          <t>2,15; 17,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 4,92</t>
+          <t>-5,94; 4,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 39,76</t>
+          <t>-9,67; 4,32</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,83</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-9,27%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 11,05</t>
+          <t>-2,65; 10,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 8,13</t>
+          <t>-2,44; 8,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 7,42</t>
+          <t>-0,88; 8,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 2,66</t>
+          <t>-3,72; 6,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 19,8</t>
+          <t>-3,89; 17,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 12,66</t>
+          <t>-3,43; 12,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 9,83</t>
+          <t>-1,07; 10,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 4,42</t>
+          <t>-5,42; 11,17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23,62</t>
+          <t>20,97</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>53,87%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 16,79</t>
+          <t>4,05; 16,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 18,19</t>
+          <t>4,65; 19,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 13,16</t>
+          <t>1,02; 13,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,3; 34,65</t>
+          <t>10,76; 31,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 39,24</t>
+          <t>7,73; 38,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,0; 38,7</t>
+          <t>8,18; 42,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 20,49</t>
+          <t>1,38; 20,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,93; 131,59</t>
+          <t>22,53; 109,3</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,02</t>
+          <t>-1,98; 2,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,35</t>
+          <t>2,48; 7,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,28</t>
+          <t>0,03; 4,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 19,34</t>
+          <t>-1,16; 3,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,13</t>
+          <t>-3,19; 4,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 12,09</t>
+          <t>3,9; 11,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 5,87</t>
+          <t>0,04; 6,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 44,59</t>
+          <t>-2,0; 6,59</t>
         </is>
       </c>
     </row>
